--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_327_R33.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_327_R33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.037</v>
+        <v>3.4073</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4776</v>
+        <v>2.7135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5595</v>
+        <v>0.6939</v>
       </c>
       <c r="G2" t="n">
         <v>1.9578</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4569</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0351</v>
+        <v>0.2008</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4217</v>
+        <v>-0.2873</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5446</v>
+        <v>2.5863</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4554</v>
+        <v>1.766</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0892</v>
+        <v>0.8203</v>
       </c>
       <c r="G3" t="n">
         <v>1.9023</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2855</v>
+        <v>-0.2438</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5975</v>
+        <v>-0.2869</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3119</v>
+        <v>0.0431</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2722</v>
+        <v>1.1959</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.259</v>
+        <v>-1.0664</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5312</v>
+        <v>2.2623</v>
       </c>
       <c r="G4" t="n">
         <v>0.9957</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1141</v>
+        <v>1.0378</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1142</v>
+        <v>0.3068</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9999</v>
+        <v>0.731</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2105</v>
+        <v>0.9252</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.114</v>
+        <v>0.0039</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3245</v>
+        <v>0.9213</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2854</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9419</v>
+        <v>0.6565</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1889</v>
+        <v>0.3068</v>
       </c>
       <c r="U5" t="n">
-        <v>0.753</v>
+        <v>0.3497</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1418</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6025</v>
+        <v>0.3172</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8253</v>
+        <v>2.3488</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2228</v>
+        <v>-2.0315</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4798</v>
+        <v>2.7269</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5041</v>
+        <v>1.6662</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9839</v>
+        <v>1.0607</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8931</v>
+        <v>3.5956</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4522</v>
+        <v>1.9529</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5591</v>
+        <v>1.6428</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3729</v>
+        <v>-0.8687</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.2866</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4248</v>
+        <v>-0.5821</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6184</v>
+        <v>0.2192</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3239</v>
+        <v>0.3973</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7055</v>
+        <v>-0.1781</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5361</v>
+        <v>-2.3969</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3612</v>
+        <v>0.3059</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6279</v>
+        <v>0.1669</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2668</v>
+        <v>0.139</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7269</v>
+        <v>-0.5966</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6662</v>
+        <v>0.4106</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0607</v>
+        <v>-1.0072</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5956</v>
+        <v>0.3005</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9529</v>
+        <v>0.6218</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6428</v>
+        <v>-0.3213</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8687</v>
+        <v>-0.897</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2866</v>
+        <v>-0.2112</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5821</v>
+        <v>-0.6859</v>
       </c>
       <c r="P7" t="n">
+        <v>1.1598</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.3917</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2631</v>
+        <v>0.168</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6765</v>
+        <v>0.0984</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4134</v>
+        <v>0.0696</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.3969</v>
+        <v>-0.4254</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.2525</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1444</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2595</v>
+        <v>-0.3082</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7517</v>
+        <v>0.6458</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0112</v>
+        <v>-0.9539</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1207</v>
+        <v>-0.4798</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3481</v>
+        <v>0.5041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2275</v>
+        <v>-0.9839</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5871</v>
+        <v>0.8931</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3564</v>
+        <v>1.4522</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2308</v>
+        <v>-0.5591</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7078</v>
+        <v>-1.3729</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7045</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0033</v>
+        <v>-0.4248</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0876</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9316</v>
+        <v>0.7077</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8363</v>
+        <v>1.1444</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0953</v>
+        <v>-0.4367</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2668</v>
+        <v>-0.6627</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3049</v>
+        <v>0.0203</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0381</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5966</v>
+        <v>-0.8781</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4106</v>
+        <v>-0.1788</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0072</v>
+        <v>-0.6993</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3005</v>
+        <v>0.0368</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6218</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3213</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.897</v>
+        <v>-0.9149</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2112</v>
+        <v>-0.1788</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6859</v>
+        <v>-0.7361</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1598</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4046</v>
+        <v>0.1612</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3734</v>
+        <v>0.1612</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0312</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4254</v>
+        <v>1.214</v>
       </c>
       <c r="W9" t="n">
+        <v>1.214</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.4254</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8986</v>
+        <v>-0.7772</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2156</v>
+        <v>-1.9996</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6830000000000001</v>
+        <v>1.2224</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8781</v>
+        <v>3.0076</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1788</v>
+        <v>0.4981</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6993</v>
+        <v>2.5095</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0368</v>
+        <v>3.2329</v>
       </c>
       <c r="K10" t="n">
+        <v>0.8773</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.3555</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.2252</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.3792</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-2.7834</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-4.871</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.0876</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.3615</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1.0722</v>
+      </c>
+      <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.0368</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.9149</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.1788</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.7361</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-1.1598</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-1.3917</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.0747</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.0747</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.214</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.214</v>
-      </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0878</v>
+        <v>-0.9536</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3102</v>
+        <v>-1.9312</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2224</v>
+        <v>0.9776</v>
       </c>
       <c r="G11" t="n">
-        <v>3.0076</v>
+        <v>-0.1207</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4981</v>
+        <v>-0.3481</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5095</v>
+        <v>0.2275</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2329</v>
+        <v>0.5871</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8773</v>
+        <v>0.3564</v>
       </c>
       <c r="L11" t="n">
-        <v>2.3555</v>
+        <v>0.2308</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2252</v>
+        <v>-0.7078</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3792</v>
+        <v>-0.7045</v>
       </c>
       <c r="O11" t="n">
-        <v>0.154</v>
+        <v>-0.0033</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.7834</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.871</v>
+        <v>-3.7112</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2399</v>
+        <v>0.7185</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6721</v>
+        <v>0.6567</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4323</v>
+        <v>0.0617</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W11" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="X11" t="n">
         <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3414</v>
+        <v>-2.644</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3342</v>
+        <v>-0.9056999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0072</v>
+        <v>-1.7383</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2529</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7328</v>
+        <v>-0.0354</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5975</v>
+        <v>-0.1689</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1353</v>
+        <v>0.1336</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8919</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6132</v>
+        <v>-4.9391</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7091</v>
+        <v>-3.0014</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9041</v>
+        <v>-1.9377</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5621</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3552</v>
+        <v>-0.6811</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8215</v>
+        <v>-0.1138</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5337</v>
+        <v>-0.5673</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.9203</v>
+        <v>-1.546999999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6125</v>
+        <v>-1.239099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3078000000000001</v>
+        <v>-0.3075999999999997</v>
       </c>
       <c r="G14" t="n">
         <v>6.414700000000001</v>
@@ -1528,7 +1528,7 @@
         <v>3.7296</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.096200000000001</v>
+        <v>-7.096199999999999</v>
       </c>
       <c r="N14" t="n">
         <v>-4.9559</v>
@@ -1546,10 +1546,10 @@
         <v>15.077</v>
       </c>
       <c r="S14" t="n">
-        <v>2.319500000000001</v>
+        <v>2.6928</v>
       </c>
       <c r="T14" t="n">
-        <v>1.968</v>
+        <v>2.3413</v>
       </c>
       <c r="U14" t="n">
         <v>0.3516</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0691</v>
+        <v>3.1981</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8458</v>
+        <v>2.7069</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2233</v>
+        <v>0.4913</v>
       </c>
       <c r="G15" t="n">
-        <v>0.311</v>
+        <v>0.0495</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.1164</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.378</v>
+        <v>-0.0668</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1769</v>
+        <v>1.8332</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9193</v>
+        <v>1.3682</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2576</v>
+        <v>0.465</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8659</v>
+        <v>-1.7837</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2303</v>
+        <v>-1.2518</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.5319</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
         <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7427</v>
+        <v>0.0068</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5272</v>
+        <v>0.2833</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2156</v>
+        <v>-0.2765</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>1.7501</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>1.7501</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3991</v>
+        <v>2.7736</v>
       </c>
       <c r="E16" t="n">
-        <v>2.471</v>
+        <v>2.2561</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9281</v>
+        <v>0.5175</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0495</v>
+        <v>0.311</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1164</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0668</v>
+        <v>-0.378</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8332</v>
+        <v>2.1769</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3682</v>
+        <v>1.9193</v>
       </c>
       <c r="L16" t="n">
-        <v>0.465</v>
+        <v>0.2576</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7837</v>
+        <v>-1.8659</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2518</v>
+        <v>-1.2303</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5319</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>2.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2078</v>
+        <v>0.4472</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0474</v>
+        <v>-0.0626</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1604</v>
+        <v>0.5098</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7501</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7501</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>F. NTILIKINA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3009</v>
+        <v>1.7427</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6469</v>
+        <v>1.1822</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.346</v>
+        <v>0.5606</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0622</v>
+        <v>0.3737</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7071</v>
+        <v>-0.5365</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3551</v>
+        <v>0.9102</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9808</v>
+        <v>0.4097</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4116</v>
+        <v>0.3361</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5692</v>
+        <v>0.0736</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9186</v>
+        <v>-0.036</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7045</v>
+        <v>-0.8726</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.214</v>
+        <v>0.8366</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.847</v>
+        <v>-1.1903</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8259</v>
+        <v>-0.2122</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0211</v>
+        <v>-0.9781</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>2.7912</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. NTILIKINA</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3388</v>
+        <v>1.4245</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9463</v>
+        <v>1.7033</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3925</v>
+        <v>-0.2788</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3737</v>
+        <v>2.0622</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5365</v>
+        <v>0.7071</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9102</v>
+        <v>1.3551</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4097</v>
+        <v>2.9808</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3361</v>
+        <v>1.4116</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0736</v>
+        <v>1.5692</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.036</v>
+        <v>-0.9186</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8726</v>
+        <v>-0.7045</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8366</v>
+        <v>-0.214</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5942</v>
+        <v>-0.0294</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4481</v>
+        <v>-0.1177</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1461</v>
+        <v>0.0883</v>
       </c>
       <c r="V18" t="n">
-        <v>2.7912</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6468</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6355</v>
+        <v>0.9247</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6209</v>
+        <v>0.9587</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0145</v>
+        <v>-0.034</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6858</v>
+        <v>-0.4733</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1644</v>
+        <v>0.1858</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4786</v>
+        <v>-0.6591</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8494</v>
+        <v>1.1208</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4383</v>
+        <v>1.4053</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5889</v>
+        <v>-0.2845</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8364</v>
+        <v>-1.5941</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7261</v>
+        <v>-1.2195</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1103</v>
+        <v>-0.3746</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3598</v>
+        <v>-0.2978</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1325</v>
+        <v>-0.0745</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.2234</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4975</v>
+        <v>0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4975</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3014</v>
+        <v>0.0958</v>
       </c>
       <c r="E20" t="n">
-        <v>0.369</v>
+        <v>-0.0868</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.1826</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4733</v>
+        <v>-1.6858</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1858</v>
+        <v>-2.1644</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6591</v>
+        <v>0.4786</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1208</v>
+        <v>-0.8494</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4053</v>
+        <v>-1.4383</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2845</v>
+        <v>0.5889</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5941</v>
+        <v>-0.8364</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2195</v>
+        <v>-0.7261</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3746</v>
+        <v>-0.1103</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9212</v>
+        <v>-0.1799</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6642</v>
+        <v>0.4248</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.257</v>
+        <v>-0.6047</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5361</v>
+        <v>1.4975</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>1.4975</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4784</v>
+        <v>-0.2761</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.178</v>
+        <v>0.0579</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3004</v>
+        <v>-0.334</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8373</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.105</v>
+        <v>0.0973</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2684</v>
+        <v>0.2348</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9802</v>
+        <v>-1.4019</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9757</v>
+        <v>-2.5654</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9955000000000001</v>
+        <v>1.1635</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7246</v>
@@ -2170,13 +2170,13 @@
         <v>2.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9221</v>
+        <v>0.5004</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9085</v>
+        <v>0.3187</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0136</v>
+        <v>0.1817</v>
       </c>
       <c r="V22" t="n">
         <v>0.6778999999999999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2346</v>
+        <v>-1.6455</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8674</v>
+        <v>-1.5136</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3672</v>
+        <v>-0.1319</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0181</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9124</v>
+        <v>-0.3233</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.315</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8783</v>
+        <v>-2.255</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0721</v>
+        <v>-2.4824</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1938</v>
+        <v>0.2274</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4135</v>
@@ -2326,13 +2326,13 @@
         <v>2.0876</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0706</v>
+        <v>-0.4472</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7389</v>
+        <v>-0.1491</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3317</v>
+        <v>-0.2981</v>
       </c>
       <c r="V24" t="n">
         <v>0.6778999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5528</v>
+        <v>-2.6606</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4989</v>
+        <v>-1.9092</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0539</v>
+        <v>-0.7514</v>
       </c>
       <c r="G25" t="n">
         <v>-1.0589</v>
@@ -2404,13 +2404,13 @@
         <v>2.5515</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7954</v>
+        <v>-0.9032</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9709</v>
+        <v>-0.3811</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8246</v>
+        <v>-0.5221</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9304</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.9205</v>
+        <v>1.920299999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3078000000000003</v>
+        <v>0.307699999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6126</v>
+        <v>1.6128</v>
       </c>
       <c r="G26" t="n">
         <v>-6.415100000000001</v>
@@ -2485,7 +2485,7 @@
         <v>-2.3194</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3515000000000001</v>
+        <v>-0.3515</v>
       </c>
       <c r="U26" t="n">
         <v>-1.968</v>
